--- a/project/outputs_xlsx_solution/prog-loop.4-wide-NC-1.xlsx
+++ b/project/outputs_xlsx_solution/prog-loop.4-wide-NC-1.xlsx
@@ -101,10 +101,10 @@
     <t>CT</t>
   </si>
   <si>
+    <t>ROB Stall</t>
+  </si>
+  <si>
     <t>RS Stall</t>
-  </si>
-  <si>
-    <t>ROB Stall</t>
   </si>
   <si>
     <t>[Legend]</t>
@@ -606,9 +606,6 @@
       <c r="AJ1">
         <v>33</v>
       </c>
-      <c r="AK1">
-        <v>34</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -833,12 +830,9 @@
         <v>15</v>
       </c>
       <c r="P9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Q9" t="s">
-        <v>14</v>
-      </c>
-      <c r="R9" t="s">
         <v>21</v>
       </c>
     </row>
@@ -864,7 +858,7 @@
       <c r="I10" t="s">
         <v>20</v>
       </c>
-      <c r="S10" t="s">
+      <c r="R10" t="s">
         <v>21</v>
       </c>
     </row>
@@ -893,7 +887,7 @@
       <c r="J11" t="s">
         <v>20</v>
       </c>
-      <c r="T11" t="s">
+      <c r="S11" t="s">
         <v>21</v>
       </c>
     </row>
@@ -922,7 +916,7 @@
       <c r="J12" t="s">
         <v>20</v>
       </c>
-      <c r="U12" t="s">
+      <c r="T12" t="s">
         <v>21</v>
       </c>
     </row>
@@ -943,15 +937,12 @@
         <v>9</v>
       </c>
       <c r="L13" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="M13" t="s">
-        <v>14</v>
-      </c>
-      <c r="N13" t="s">
-        <v>20</v>
-      </c>
-      <c r="V13" t="s">
+        <v>20</v>
+      </c>
+      <c r="U13" t="s">
         <v>21</v>
       </c>
     </row>
@@ -974,6 +965,9 @@
       <c r="L14" t="s">
         <v>16</v>
       </c>
+      <c r="M14" t="s">
+        <v>14</v>
+      </c>
       <c r="N14" t="s">
         <v>14</v>
       </c>
@@ -984,12 +978,9 @@
         <v>14</v>
       </c>
       <c r="Q14" t="s">
-        <v>14</v>
-      </c>
-      <c r="R14" t="s">
-        <v>20</v>
-      </c>
-      <c r="W14" t="s">
+        <v>20</v>
+      </c>
+      <c r="V14" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1010,18 +1001,15 @@
         <v>9</v>
       </c>
       <c r="L15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N15" t="s">
-        <v>14</v>
-      </c>
-      <c r="O15" t="s">
-        <v>20</v>
-      </c>
-      <c r="X15" t="s">
+        <v>20</v>
+      </c>
+      <c r="W15" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1044,6 +1032,9 @@
       <c r="L16" t="s">
         <v>16</v>
       </c>
+      <c r="Q16" t="s">
+        <v>14</v>
+      </c>
       <c r="R16" t="s">
         <v>14</v>
       </c>
@@ -1051,12 +1042,9 @@
         <v>14</v>
       </c>
       <c r="T16" t="s">
-        <v>14</v>
-      </c>
-      <c r="U16" t="s">
-        <v>20</v>
-      </c>
-      <c r="Y16" t="s">
+        <v>20</v>
+      </c>
+      <c r="X16" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1079,13 +1067,13 @@
       <c r="M17" t="s">
         <v>16</v>
       </c>
+      <c r="T17" t="s">
+        <v>14</v>
+      </c>
       <c r="U17" t="s">
-        <v>14</v>
-      </c>
-      <c r="V17" t="s">
-        <v>20</v>
-      </c>
-      <c r="Z17" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y17" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1106,15 +1094,12 @@
         <v>9</v>
       </c>
       <c r="M18" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N18" t="s">
-        <v>14</v>
-      </c>
-      <c r="O18" t="s">
-        <v>20</v>
-      </c>
-      <c r="AA18" t="s">
+        <v>20</v>
+      </c>
+      <c r="Z18" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1135,18 +1120,15 @@
         <v>9</v>
       </c>
       <c r="M19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O19" t="s">
-        <v>14</v>
-      </c>
-      <c r="P19" t="s">
-        <v>20</v>
-      </c>
-      <c r="AB19" t="s">
+        <v>20</v>
+      </c>
+      <c r="AA19" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1169,13 +1151,13 @@
       <c r="M20" t="s">
         <v>16</v>
       </c>
+      <c r="N20" t="s">
+        <v>14</v>
+      </c>
       <c r="O20" t="s">
-        <v>14</v>
-      </c>
-      <c r="P20" t="s">
-        <v>20</v>
-      </c>
-      <c r="AC20" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB20" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1196,15 +1178,12 @@
         <v>9</v>
       </c>
       <c r="N21" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="O21" t="s">
-        <v>14</v>
-      </c>
-      <c r="P21" t="s">
-        <v>20</v>
-      </c>
-      <c r="AD21" t="s">
+        <v>20</v>
+      </c>
+      <c r="AC21" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1227,11 +1206,14 @@
       <c r="N22" t="s">
         <v>16</v>
       </c>
+      <c r="O22" t="s">
+        <v>15</v>
+      </c>
       <c r="P22" t="s">
         <v>15</v>
       </c>
       <c r="Q22" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R22" t="s">
         <v>14</v>
@@ -1243,12 +1225,9 @@
         <v>14</v>
       </c>
       <c r="U22" t="s">
-        <v>14</v>
-      </c>
-      <c r="V22" t="s">
-        <v>20</v>
-      </c>
-      <c r="AE22" t="s">
+        <v>20</v>
+      </c>
+      <c r="AD22" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1269,18 +1248,15 @@
         <v>9</v>
       </c>
       <c r="N23" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="O23" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="P23" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>20</v>
-      </c>
-      <c r="AF23" t="s">
+        <v>20</v>
+      </c>
+      <c r="AE23" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1300,9 +1276,15 @@
       <c r="M24" t="s">
         <v>9</v>
       </c>
+      <c r="N24" t="s">
+        <v>22</v>
+      </c>
       <c r="O24" t="s">
         <v>16</v>
       </c>
+      <c r="U24" t="s">
+        <v>14</v>
+      </c>
       <c r="V24" t="s">
         <v>14</v>
       </c>
@@ -1310,12 +1292,9 @@
         <v>14</v>
       </c>
       <c r="X24" t="s">
-        <v>14</v>
-      </c>
-      <c r="Y24" t="s">
-        <v>20</v>
-      </c>
-      <c r="AG24" t="s">
+        <v>20</v>
+      </c>
+      <c r="AF24" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1336,24 +1315,21 @@
         <v>9</v>
       </c>
       <c r="O25" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P25" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q25" t="s">
-        <v>22</v>
-      </c>
-      <c r="R25" t="s">
-        <v>16</v>
+        <v>16</v>
+      </c>
+      <c r="X25" t="s">
+        <v>14</v>
       </c>
       <c r="Y25" t="s">
-        <v>14</v>
-      </c>
-      <c r="Z25" t="s">
-        <v>20</v>
-      </c>
-      <c r="AH25" t="s">
+        <v>20</v>
+      </c>
+      <c r="AG25" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1373,19 +1349,16 @@
       <c r="N26" t="s">
         <v>9</v>
       </c>
+      <c r="Q26" t="s">
+        <v>22</v>
+      </c>
       <c r="R26" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="S26" t="s">
-        <v>16</v>
-      </c>
-      <c r="T26" t="s">
-        <v>14</v>
-      </c>
-      <c r="U26" t="s">
-        <v>20</v>
-      </c>
-      <c r="AI26" t="s">
+        <v>20</v>
+      </c>
+      <c r="AH26" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1405,19 +1378,16 @@
       <c r="N27" t="s">
         <v>9</v>
       </c>
+      <c r="R27" t="s">
+        <v>22</v>
+      </c>
       <c r="S27" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="T27" t="s">
-        <v>16</v>
-      </c>
-      <c r="U27" t="s">
-        <v>14</v>
-      </c>
-      <c r="V27" t="s">
-        <v>20</v>
-      </c>
-      <c r="AJ27" t="s">
+        <v>20</v>
+      </c>
+      <c r="AI27" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1437,19 +1407,16 @@
       <c r="N28" t="s">
         <v>9</v>
       </c>
+      <c r="S28" t="s">
+        <v>22</v>
+      </c>
       <c r="T28" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="U28" t="s">
-        <v>16</v>
-      </c>
-      <c r="V28" t="s">
-        <v>14</v>
-      </c>
-      <c r="W28" t="s">
-        <v>20</v>
-      </c>
-      <c r="AK28" t="s">
+        <v>20</v>
+      </c>
+      <c r="AJ28" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1508,7 +1475,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B37" t="s">
         <v>31</v>
@@ -1516,7 +1483,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B38" t="s">
         <v>32</v>
